--- a/data/publications/handbook-statistics-on-indian-economy/annual-series/output-and-prices/Minimum Support Price for Non-Foodgrains According to Crop Year (Fair Average Quality).xlsx
+++ b/data/publications/handbook-statistics-on-indian-economy/annual-series/output-and-prices/Minimum Support Price for Non-Foodgrains According to Crop Year (Fair Average Quality).xlsx
@@ -8,7 +8,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="66">
   <si>
     <t>Year</t>
   </si>
@@ -40,12 +40,15 @@
     <t>Safflower</t>
   </si>
   <si>
+    <t xml:space="preserve">2026-27   </t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
     <t xml:space="preserve">2025-26   </t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t xml:space="preserve">2024-25   </t>
   </si>
   <si>
@@ -202,15 +205,15 @@
     <t>(Rupees per Quintal)</t>
   </si>
   <si>
-    <t xml:space="preserve">Notes :    1. For Sugarcane upto 2004-05 Statutory Minimum Price(SMP) linked to a basic recovery of 8.5 per cent of sugar with proportionate
-                   premium for every 0.1 per cent increase in recovery above that level. The SMP for 2002-03 includes the one time drought relief.
-               2. Minimum Support Price (MSP) of cotton for H-4.
-               3. Cotton for 2006-07 and onwards are long Staple.
-               4. Groundnut(inshell), Soyabean Yellow, Soyabean black for 2017-18 includes a bonus of Rs 200, Sunflower seed and Safflower
-                   seed includes bonus of Rs 100 over and above MSP.
-               5. Groundnut, Soyabean black, Soyabean Yellow, Rapeseed &amp; Mustard, Sunflower seed and Safflower seed included a bonus of Rs 100 for 2016-17.
-Also see Notes on Tables.
-Sources :  1. Ministry of Agriculture &amp; Farmers Welfare, Government of India.
+    <t xml:space="preserve">Notes    : 1. For Sugarcane upto 2004-05 Statutory Minimum Price (SMP) linked to a basic recovery of 8.5 per cent of sugar with proportionate premium for 
+                   every 0.1 per cent increase in recovery above that level. The SMP for 2002-03 includes the one time drought relief.
+                2. Minimum Support Price (MSP) of cotton for H-4.
+                3. Cotton from 2006-07 and onwards is long Staple.
+                4. Groundnut (inshell), Soyabean Yellow, Soyabean black for 2017-18 includes a bonus of ₹ 200, Sunflower seed and Safflower seed includes bonus 
+                   of ₹ 100 over and above MSP.
+                5. Groundnut, Soyabean black, Soyabean Yellow, Rapeseed &amp; Mustard, Sunflower seed and Safflower seed included a bonus of ₹ 100 for 2016-17.
+                   Also see Notes on Tables.
+Sources : 1 .Ministry of Agriculture &amp; Farmers Welfare, Government of India.
                 2. Economic Survey 2011-12, Government of India.</t>
   </si>
 </sst>
@@ -397,7 +400,7 @@
     <xf numFmtId="49" fontId="3" fillId="4" borderId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="4" fillId="4" borderId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="4" fillId="2" borderId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="2" borderId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -415,19 +418,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L60"/>
+  <dimension ref="A1:M62"/>
   <cols>
     <col min="1" max="1" width="4.67767866666667" customWidth="1"/>
     <col min="2" max="2" width="14.701508" customWidth="1"/>
     <col min="3" max="11" width="11.1231986666667" customWidth="1"/>
     <col min="12" max="12" width="86736e-6" customWidth="1"/>
     <col min="13" max="13" width="834000e-6" customWidth="1"/>
+    <col min="14" max="14" width="4.67767866666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="14.3991" customHeight="1"/>
     <row r="2" s="1" customFormat="1" ht="31.998" customHeight="1">
       <c r="B2" s="11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C2" s="11"/>
       <c r="D2" s="11"/>
@@ -443,7 +447,7 @@
     <row r="3" s="1" customFormat="1" ht="6.9329" customHeight="1"/>
     <row r="4" s="1" customFormat="1" ht="15.999" customHeight="1">
       <c r="B4" s="12" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C4" s="12"/>
     </row>
@@ -517,25 +521,25 @@
         <v>10</v>
       </c>
       <c r="C8" s="7">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="D8" s="7">
-        <v>8110</v>
+        <v>8667</v>
       </c>
       <c r="E8" s="7">
-        <v>5650</v>
+        <v>5925</v>
       </c>
       <c r="F8" s="7">
-        <v>7263</v>
+        <v>7517</v>
       </c>
       <c r="G8" s="7" t="s">
         <v>11</v>
       </c>
       <c r="H8" s="7">
-        <v>5328</v>
+        <v>5708</v>
       </c>
       <c r="I8" s="7">
-        <v>7721</v>
+        <v>8343</v>
       </c>
       <c r="J8" s="7" t="s">
         <v>11</v>
@@ -549,31 +553,31 @@
         <v>12</v>
       </c>
       <c r="C9" s="8">
-        <v>340</v>
+        <v>355</v>
       </c>
       <c r="D9" s="8">
-        <v>7521</v>
+        <v>8110</v>
       </c>
       <c r="E9" s="8">
-        <v>5335</v>
+        <v>5650</v>
       </c>
       <c r="F9" s="8">
-        <v>6783</v>
+        <v>7263</v>
       </c>
       <c r="G9" s="8" t="s">
         <v>11</v>
       </c>
       <c r="H9" s="8">
-        <v>4892</v>
+        <v>5328</v>
       </c>
       <c r="I9" s="8">
-        <v>7280</v>
+        <v>7721</v>
       </c>
       <c r="J9" s="8">
-        <v>5950</v>
+        <v>6200</v>
       </c>
       <c r="K9" s="8">
-        <v>5940</v>
+        <v>6540</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="18.6655" customHeight="1">
@@ -581,31 +585,31 @@
         <v>13</v>
       </c>
       <c r="C10" s="7">
-        <v>315</v>
+        <v>340</v>
       </c>
       <c r="D10" s="7">
-        <v>7020</v>
+        <v>7521</v>
       </c>
       <c r="E10" s="7">
-        <v>5050</v>
+        <v>5335</v>
       </c>
       <c r="F10" s="7">
-        <v>6377</v>
+        <v>6783</v>
       </c>
       <c r="G10" s="7" t="s">
         <v>11</v>
       </c>
       <c r="H10" s="7">
-        <v>4600</v>
+        <v>4892</v>
       </c>
       <c r="I10" s="7">
-        <v>6760</v>
+        <v>7280</v>
       </c>
       <c r="J10" s="7">
-        <v>5650</v>
+        <v>5950</v>
       </c>
       <c r="K10" s="7">
-        <v>5800</v>
+        <v>5940</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="18.6655" customHeight="1">
@@ -613,31 +617,31 @@
         <v>14</v>
       </c>
       <c r="C11" s="8">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="D11" s="8">
-        <v>6380</v>
+        <v>7020</v>
       </c>
       <c r="E11" s="8">
-        <v>4750</v>
+        <v>5050</v>
       </c>
       <c r="F11" s="8">
-        <v>5850</v>
+        <v>6377</v>
       </c>
       <c r="G11" s="8" t="s">
         <v>11</v>
       </c>
       <c r="H11" s="8">
-        <v>4300</v>
+        <v>4600</v>
       </c>
       <c r="I11" s="8">
-        <v>6400</v>
+        <v>6760</v>
       </c>
       <c r="J11" s="8">
-        <v>5450</v>
+        <v>5650</v>
       </c>
       <c r="K11" s="8">
-        <v>5650</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="18.6655" customHeight="1">
@@ -645,31 +649,31 @@
         <v>15</v>
       </c>
       <c r="C12" s="7">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="D12" s="7">
-        <v>6025</v>
+        <v>6380</v>
       </c>
       <c r="E12" s="7">
-        <v>4500</v>
+        <v>4750</v>
       </c>
       <c r="F12" s="7">
-        <v>5550</v>
+        <v>5850</v>
       </c>
       <c r="G12" s="7" t="s">
         <v>11</v>
       </c>
       <c r="H12" s="7">
-        <v>3950</v>
+        <v>4300</v>
       </c>
       <c r="I12" s="7">
-        <v>6015</v>
+        <v>6400</v>
       </c>
       <c r="J12" s="7">
-        <v>5050</v>
+        <v>5450</v>
       </c>
       <c r="K12" s="7">
-        <v>5441</v>
+        <v>5650</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="18.6655" customHeight="1">
@@ -677,31 +681,31 @@
         <v>16</v>
       </c>
       <c r="C13" s="8">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="D13" s="8">
-        <v>5825</v>
+        <v>6025</v>
       </c>
       <c r="E13" s="8">
-        <v>4225</v>
+        <v>4500</v>
       </c>
       <c r="F13" s="8">
-        <v>5275</v>
+        <v>5550</v>
       </c>
       <c r="G13" s="8" t="s">
         <v>11</v>
       </c>
       <c r="H13" s="8">
-        <v>3880</v>
+        <v>3950</v>
       </c>
       <c r="I13" s="8">
-        <v>5885</v>
+        <v>6015</v>
       </c>
       <c r="J13" s="8">
-        <v>4650</v>
+        <v>5050</v>
       </c>
       <c r="K13" s="8">
-        <v>5327</v>
+        <v>5441</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="18.6655" customHeight="1">
@@ -709,31 +713,31 @@
         <v>17</v>
       </c>
       <c r="C14" s="7">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="D14" s="7">
-        <v>5550</v>
+        <v>5825</v>
       </c>
       <c r="E14" s="7">
-        <v>3950</v>
+        <v>4225</v>
       </c>
       <c r="F14" s="7">
-        <v>5090</v>
+        <v>5275</v>
       </c>
       <c r="G14" s="7" t="s">
         <v>11</v>
       </c>
       <c r="H14" s="7">
-        <v>3710</v>
+        <v>3880</v>
       </c>
       <c r="I14" s="7">
-        <v>5650</v>
+        <v>5885</v>
       </c>
       <c r="J14" s="7">
-        <v>4425</v>
+        <v>4650</v>
       </c>
       <c r="K14" s="7">
-        <v>5215</v>
+        <v>5327</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" ht="18.6655" customHeight="1">
@@ -744,28 +748,28 @@
         <v>275</v>
       </c>
       <c r="D15" s="8">
-        <v>5450</v>
+        <v>5550</v>
       </c>
       <c r="E15" s="8">
-        <v>3700</v>
+        <v>3950</v>
       </c>
       <c r="F15" s="8">
-        <v>4890</v>
+        <v>5090</v>
       </c>
       <c r="G15" s="8" t="s">
         <v>11</v>
       </c>
       <c r="H15" s="8">
-        <v>3399</v>
+        <v>3710</v>
       </c>
       <c r="I15" s="8">
-        <v>5388</v>
+        <v>5650</v>
       </c>
       <c r="J15" s="8">
-        <v>4200</v>
+        <v>4425</v>
       </c>
       <c r="K15" s="8">
-        <v>4945</v>
+        <v>5215</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" ht="18.6655" customHeight="1">
@@ -773,31 +777,31 @@
         <v>19</v>
       </c>
       <c r="C16" s="7">
-        <v>255</v>
+        <v>275</v>
       </c>
       <c r="D16" s="7">
-        <v>4320</v>
+        <v>5450</v>
       </c>
       <c r="E16" s="7">
-        <v>3500</v>
+        <v>3700</v>
       </c>
       <c r="F16" s="7">
-        <v>4450</v>
+        <v>4890</v>
       </c>
       <c r="G16" s="7" t="s">
         <v>11</v>
       </c>
       <c r="H16" s="7">
-        <v>3050</v>
+        <v>3399</v>
       </c>
       <c r="I16" s="7">
-        <v>4100</v>
+        <v>5388</v>
       </c>
       <c r="J16" s="7">
-        <v>4000</v>
+        <v>4200</v>
       </c>
       <c r="K16" s="7">
-        <v>4100</v>
+        <v>4945</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="18.6655" customHeight="1">
@@ -805,31 +809,31 @@
         <v>20</v>
       </c>
       <c r="C17" s="8">
-        <v>230</v>
+        <v>255</v>
       </c>
       <c r="D17" s="8">
-        <v>4160</v>
+        <v>4320</v>
       </c>
       <c r="E17" s="8">
-        <v>3200</v>
+        <v>3500</v>
       </c>
       <c r="F17" s="8">
-        <v>4220</v>
-      </c>
-      <c r="G17" s="8">
-        <v>2775</v>
+        <v>4450</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="H17" s="8">
-        <v>2775</v>
+        <v>3050</v>
       </c>
       <c r="I17" s="8">
-        <v>3950</v>
+        <v>4100</v>
       </c>
       <c r="J17" s="8">
-        <v>3700</v>
+        <v>4000</v>
       </c>
       <c r="K17" s="8">
-        <v>3700</v>
+        <v>4100</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="18.6655" customHeight="1">
@@ -840,28 +844,28 @@
         <v>230</v>
       </c>
       <c r="D18" s="7">
-        <v>4100</v>
+        <v>4160</v>
       </c>
       <c r="E18" s="7">
-        <v>2700</v>
+        <v>3200</v>
       </c>
       <c r="F18" s="7">
-        <v>4030</v>
-      </c>
-      <c r="G18" s="7" t="s">
-        <v>11</v>
+        <v>4220</v>
+      </c>
+      <c r="G18" s="7">
+        <v>2775</v>
       </c>
       <c r="H18" s="7">
-        <v>2600</v>
+        <v>2775</v>
       </c>
       <c r="I18" s="7">
-        <v>3800</v>
+        <v>3950</v>
       </c>
       <c r="J18" s="7">
-        <v>3350</v>
+        <v>3700</v>
       </c>
       <c r="K18" s="7">
-        <v>3300</v>
+        <v>3700</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" ht="18.6655" customHeight="1">
@@ -869,31 +873,31 @@
         <v>22</v>
       </c>
       <c r="C19" s="8">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="D19" s="8">
-        <v>4050</v>
+        <v>4100</v>
       </c>
       <c r="E19" s="8">
-        <v>2400</v>
+        <v>2700</v>
       </c>
       <c r="F19" s="8">
-        <v>4000</v>
-      </c>
-      <c r="G19" s="8">
-        <v>2500</v>
+        <v>4030</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="H19" s="8">
-        <v>2560</v>
+        <v>2600</v>
       </c>
       <c r="I19" s="8">
-        <v>3750</v>
+        <v>3800</v>
       </c>
       <c r="J19" s="8">
-        <v>3100</v>
+        <v>3350</v>
       </c>
       <c r="K19" s="8">
-        <v>3050</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" ht="18.6655" customHeight="1">
@@ -901,13 +905,13 @@
         <v>23</v>
       </c>
       <c r="C20" s="7">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="D20" s="7">
-        <v>4000</v>
+        <v>4050</v>
       </c>
       <c r="E20" s="7">
-        <v>2300</v>
+        <v>2400</v>
       </c>
       <c r="F20" s="7">
         <v>4000</v>
@@ -919,13 +923,13 @@
         <v>2560</v>
       </c>
       <c r="I20" s="7">
-        <v>3700</v>
+        <v>3750</v>
       </c>
       <c r="J20" s="7">
+        <v>3100</v>
+      </c>
+      <c r="K20" s="7">
         <v>3050</v>
-      </c>
-      <c r="K20" s="7">
-        <v>3000</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" ht="18.6655" customHeight="1">
@@ -933,31 +937,31 @@
         <v>24</v>
       </c>
       <c r="C21" s="8">
-        <v>170</v>
+        <v>210</v>
       </c>
       <c r="D21" s="8">
-        <v>3900</v>
+        <v>4000</v>
       </c>
       <c r="E21" s="8">
-        <v>2200</v>
+        <v>2300</v>
       </c>
       <c r="F21" s="8">
-        <v>3700</v>
+        <v>4000</v>
       </c>
       <c r="G21" s="8">
-        <v>2200</v>
+        <v>2500</v>
       </c>
       <c r="H21" s="8">
-        <v>2240</v>
+        <v>2560</v>
       </c>
       <c r="I21" s="8">
         <v>3700</v>
       </c>
       <c r="J21" s="8">
+        <v>3050</v>
+      </c>
+      <c r="K21" s="8">
         <v>3000</v>
-      </c>
-      <c r="K21" s="8">
-        <v>2800</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" ht="18.6655" customHeight="1">
@@ -965,31 +969,31 @@
         <v>25</v>
       </c>
       <c r="C22" s="7">
-        <v>145</v>
+        <v>170</v>
       </c>
       <c r="D22" s="7">
-        <v>3300</v>
+        <v>3900</v>
       </c>
       <c r="E22" s="7">
-        <v>1675</v>
+        <v>2200</v>
       </c>
       <c r="F22" s="7">
-        <v>2700</v>
+        <v>3700</v>
       </c>
       <c r="G22" s="7">
-        <v>1650</v>
+        <v>2200</v>
       </c>
       <c r="H22" s="7">
-        <v>1690</v>
+        <v>2240</v>
       </c>
       <c r="I22" s="7">
+        <v>3700</v>
+      </c>
+      <c r="J22" s="7">
+        <v>3000</v>
+      </c>
+      <c r="K22" s="7">
         <v>2800</v>
-      </c>
-      <c r="J22" s="7">
-        <v>2500</v>
-      </c>
-      <c r="K22" s="7">
-        <v>2500</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" ht="18.6655" customHeight="1">
@@ -997,31 +1001,31 @@
         <v>26</v>
       </c>
       <c r="C23" s="8">
-        <v>139.12</v>
+        <v>145</v>
       </c>
       <c r="D23" s="8">
-        <v>3000</v>
+        <v>3300</v>
       </c>
       <c r="E23" s="8">
-        <v>1575</v>
+        <v>1675</v>
       </c>
       <c r="F23" s="8">
-        <v>2300</v>
+        <v>2700</v>
       </c>
       <c r="G23" s="8">
-        <v>1400</v>
+        <v>1650</v>
       </c>
       <c r="H23" s="8">
-        <v>1440</v>
+        <v>1690</v>
       </c>
       <c r="I23" s="8">
-        <v>2350</v>
+        <v>2800</v>
       </c>
       <c r="J23" s="8">
-        <v>1850</v>
+        <v>2500</v>
       </c>
       <c r="K23" s="8">
-        <v>1800</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" ht="18.6655" customHeight="1">
@@ -1029,31 +1033,31 @@
         <v>27</v>
       </c>
       <c r="C24" s="7">
-        <v>129.84</v>
+        <v>139.12</v>
       </c>
       <c r="D24" s="7">
         <v>3000</v>
       </c>
       <c r="E24" s="7">
-        <v>1375</v>
+        <v>1575</v>
       </c>
       <c r="F24" s="7">
-        <v>2100</v>
+        <v>2300</v>
       </c>
       <c r="G24" s="7">
-        <v>1350</v>
+        <v>1400</v>
       </c>
       <c r="H24" s="7">
-        <v>1390</v>
+        <v>1440</v>
       </c>
       <c r="I24" s="7">
-        <v>2215</v>
+        <v>2350</v>
       </c>
       <c r="J24" s="7">
-        <v>1830</v>
+        <v>1850</v>
       </c>
       <c r="K24" s="7">
-        <v>1680</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" ht="18.6655" customHeight="1">
@@ -1061,13 +1065,13 @@
         <v>28</v>
       </c>
       <c r="C25" s="8">
-        <v>81.18</v>
+        <v>129.84</v>
       </c>
       <c r="D25" s="8">
         <v>3000</v>
       </c>
       <c r="E25" s="8">
-        <v>1250</v>
+        <v>1375</v>
       </c>
       <c r="F25" s="8">
         <v>2100</v>
@@ -1085,7 +1089,7 @@
         <v>1830</v>
       </c>
       <c r="K25" s="8">
-        <v>1650</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="18.6655" customHeight="1">
@@ -1096,25 +1100,25 @@
         <v>81.18</v>
       </c>
       <c r="D26" s="7">
-        <v>2030</v>
+        <v>3000</v>
       </c>
       <c r="E26" s="7">
-        <v>1055</v>
+        <v>1250</v>
       </c>
       <c r="F26" s="7">
-        <v>1550</v>
+        <v>2100</v>
       </c>
       <c r="G26" s="7">
-        <v>910</v>
+        <v>1350</v>
       </c>
       <c r="H26" s="7">
-        <v>1050</v>
+        <v>1390</v>
       </c>
       <c r="I26" s="7">
-        <v>1510</v>
+        <v>2215</v>
       </c>
       <c r="J26" s="7">
-        <v>1800</v>
+        <v>1830</v>
       </c>
       <c r="K26" s="7">
         <v>1650</v>
@@ -1125,31 +1129,31 @@
         <v>30</v>
       </c>
       <c r="C27" s="8">
-        <v>80.25</v>
+        <v>81.18</v>
       </c>
       <c r="D27" s="8">
-        <v>1990</v>
+        <v>2030</v>
       </c>
       <c r="E27" s="8">
-        <v>1000</v>
+        <v>1055</v>
       </c>
       <c r="F27" s="8">
-        <v>1520</v>
+        <v>1550</v>
       </c>
       <c r="G27" s="8">
-        <v>900</v>
+        <v>910</v>
       </c>
       <c r="H27" s="8">
-        <v>1020</v>
+        <v>1050</v>
       </c>
       <c r="I27" s="8">
-        <v>1500</v>
+        <v>1510</v>
       </c>
       <c r="J27" s="8">
-        <v>1715</v>
+        <v>1800</v>
       </c>
       <c r="K27" s="8">
-        <v>1565</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" ht="18.6655" customHeight="1">
@@ -1157,13 +1161,13 @@
         <v>31</v>
       </c>
       <c r="C28" s="7">
-        <v>79.5</v>
+        <v>80.25</v>
       </c>
       <c r="D28" s="7">
-        <v>1980</v>
+        <v>1990</v>
       </c>
       <c r="E28" s="7">
-        <v>910</v>
+        <v>1000</v>
       </c>
       <c r="F28" s="7">
         <v>1520</v>
@@ -1172,7 +1176,7 @@
         <v>900</v>
       </c>
       <c r="H28" s="7">
-        <v>1010</v>
+        <v>1020</v>
       </c>
       <c r="I28" s="7">
         <v>1500</v>
@@ -1189,31 +1193,31 @@
         <v>32</v>
       </c>
       <c r="C29" s="8">
-        <v>74.5</v>
+        <v>79.5</v>
       </c>
       <c r="D29" s="8">
-        <v>1960</v>
+        <v>1980</v>
       </c>
       <c r="E29" s="8">
-        <v>890</v>
+        <v>910</v>
       </c>
       <c r="F29" s="8">
-        <v>1500</v>
+        <v>1520</v>
       </c>
       <c r="G29" s="8">
         <v>900</v>
       </c>
       <c r="H29" s="8">
-        <v>1000</v>
+        <v>1010</v>
       </c>
       <c r="I29" s="8">
-        <v>1340</v>
+        <v>1500</v>
       </c>
       <c r="J29" s="8">
-        <v>1700</v>
+        <v>1715</v>
       </c>
       <c r="K29" s="8">
-        <v>1550</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" ht="18.6655" customHeight="1">
@@ -1221,31 +1225,31 @@
         <v>33</v>
       </c>
       <c r="C30" s="7">
-        <v>73</v>
+        <v>74.5</v>
       </c>
       <c r="D30" s="7">
-        <v>1925</v>
+        <v>1960</v>
       </c>
       <c r="E30" s="7">
-        <v>860</v>
+        <v>890</v>
       </c>
       <c r="F30" s="7">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="G30" s="7">
-        <v>840</v>
+        <v>900</v>
       </c>
       <c r="H30" s="7">
-        <v>930</v>
+        <v>1000</v>
       </c>
       <c r="I30" s="7">
-        <v>1250</v>
+        <v>1340</v>
       </c>
       <c r="J30" s="7">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="K30" s="7">
-        <v>1500</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" ht="18.6655" customHeight="1">
@@ -1253,31 +1257,31 @@
         <v>34</v>
       </c>
       <c r="C31" s="8">
-        <v>69.5</v>
+        <v>73</v>
       </c>
       <c r="D31" s="8">
-        <v>1875</v>
+        <v>1925</v>
       </c>
       <c r="E31" s="8">
-        <v>850</v>
+        <v>860</v>
       </c>
       <c r="F31" s="8">
-        <v>1355</v>
+        <v>1400</v>
       </c>
       <c r="G31" s="8">
-        <v>795</v>
+        <v>840</v>
       </c>
       <c r="H31" s="8">
-        <v>885</v>
+        <v>930</v>
       </c>
       <c r="I31" s="8">
-        <v>1195</v>
+        <v>1250</v>
       </c>
       <c r="J31" s="8">
-        <v>1330</v>
+        <v>1600</v>
       </c>
       <c r="K31" s="8">
-        <v>1300</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" ht="18.6655" customHeight="1">
@@ -1285,16 +1289,16 @@
         <v>35</v>
       </c>
       <c r="C32" s="7">
-        <v>62.05</v>
+        <v>69.5</v>
       </c>
       <c r="D32" s="7">
         <v>1875</v>
       </c>
       <c r="E32" s="7">
-        <v>810</v>
+        <v>850</v>
       </c>
       <c r="F32" s="7">
-        <v>1340</v>
+        <v>1355</v>
       </c>
       <c r="G32" s="7">
         <v>795</v>
@@ -1303,10 +1307,10 @@
         <v>885</v>
       </c>
       <c r="I32" s="7">
-        <v>1185</v>
+        <v>1195</v>
       </c>
       <c r="J32" s="7">
-        <v>1300</v>
+        <v>1330</v>
       </c>
       <c r="K32" s="7">
         <v>1300</v>
@@ -1317,31 +1321,31 @@
         <v>36</v>
       </c>
       <c r="C33" s="8">
-        <v>59.5</v>
+        <v>62.05</v>
       </c>
       <c r="D33" s="8">
-        <v>1825</v>
+        <v>1875</v>
       </c>
       <c r="E33" s="8">
-        <v>785</v>
+        <v>810</v>
       </c>
       <c r="F33" s="8">
-        <v>1220</v>
+        <v>1340</v>
       </c>
       <c r="G33" s="8">
-        <v>775</v>
+        <v>795</v>
       </c>
       <c r="H33" s="8">
-        <v>865</v>
+        <v>885</v>
       </c>
       <c r="I33" s="8">
-        <v>1170</v>
+        <v>1185</v>
       </c>
       <c r="J33" s="8">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="K33" s="8">
-        <v>1200</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" ht="18.6655" customHeight="1">
@@ -1349,31 +1353,31 @@
         <v>37</v>
       </c>
       <c r="C34" s="7">
-        <v>56.1</v>
+        <v>59.5</v>
       </c>
       <c r="D34" s="7">
-        <v>1775</v>
+        <v>1825</v>
       </c>
       <c r="E34" s="7">
-        <v>750</v>
+        <v>785</v>
       </c>
       <c r="F34" s="7">
-        <v>1155</v>
+        <v>1220</v>
       </c>
       <c r="G34" s="7">
-        <v>755</v>
+        <v>775</v>
       </c>
       <c r="H34" s="7">
-        <v>845</v>
+        <v>865</v>
       </c>
       <c r="I34" s="7">
-        <v>1155</v>
+        <v>1170</v>
       </c>
       <c r="J34" s="7">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="K34" s="7">
-        <v>1100</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" ht="18.6655" customHeight="1">
@@ -1381,31 +1385,31 @@
         <v>38</v>
       </c>
       <c r="C35" s="8">
-        <v>52.7</v>
+        <v>56.1</v>
       </c>
       <c r="D35" s="8">
-        <v>1650</v>
+        <v>1775</v>
       </c>
       <c r="E35" s="8">
-        <v>650</v>
+        <v>750</v>
       </c>
       <c r="F35" s="8">
-        <v>1040</v>
+        <v>1155</v>
       </c>
       <c r="G35" s="8">
-        <v>705</v>
+        <v>755</v>
       </c>
       <c r="H35" s="8">
-        <v>795</v>
+        <v>845</v>
       </c>
       <c r="I35" s="8">
-        <v>1060</v>
+        <v>1155</v>
       </c>
       <c r="J35" s="8">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="K35" s="8">
-        <v>990</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" ht="18.6655" customHeight="1">
@@ -1413,31 +1417,31 @@
         <v>39</v>
       </c>
       <c r="C36" s="7">
-        <v>48.45</v>
+        <v>52.7</v>
       </c>
       <c r="D36" s="7">
-        <v>1530</v>
+        <v>1650</v>
       </c>
       <c r="E36" s="7">
-        <v>570</v>
+        <v>650</v>
       </c>
       <c r="F36" s="7">
-        <v>980</v>
+        <v>1040</v>
       </c>
       <c r="G36" s="7">
-        <v>670</v>
+        <v>705</v>
       </c>
       <c r="H36" s="7">
-        <v>750</v>
+        <v>795</v>
       </c>
       <c r="I36" s="7">
+        <v>1060</v>
+      </c>
+      <c r="J36" s="7">
         <v>1000</v>
       </c>
-      <c r="J36" s="7">
-        <v>940</v>
-      </c>
       <c r="K36" s="7">
-        <v>910</v>
+        <v>990</v>
       </c>
     </row>
     <row r="37" s="1" customFormat="1" ht="18.6655" customHeight="1">
@@ -1445,31 +1449,31 @@
         <v>40</v>
       </c>
       <c r="C37" s="8">
-        <v>45.9</v>
+        <v>48.45</v>
       </c>
       <c r="D37" s="8">
-        <v>1380</v>
+        <v>1530</v>
       </c>
       <c r="E37" s="8">
-        <v>510</v>
+        <v>570</v>
       </c>
       <c r="F37" s="8">
-        <v>920</v>
+        <v>980</v>
       </c>
       <c r="G37" s="8">
-        <v>620</v>
+        <v>670</v>
       </c>
       <c r="H37" s="8">
-        <v>700</v>
+        <v>750</v>
       </c>
       <c r="I37" s="8">
-        <v>960</v>
+        <v>1000</v>
       </c>
       <c r="J37" s="8">
-        <v>890</v>
+        <v>940</v>
       </c>
       <c r="K37" s="8">
-        <v>830</v>
+        <v>910</v>
       </c>
     </row>
     <row r="38" s="1" customFormat="1" ht="18.6655" customHeight="1">
@@ -1477,31 +1481,31 @@
         <v>41</v>
       </c>
       <c r="C38" s="7">
-        <v>42.5</v>
+        <v>45.9</v>
       </c>
       <c r="D38" s="7">
-        <v>1350</v>
+        <v>1380</v>
       </c>
       <c r="E38" s="7">
-        <v>490</v>
+        <v>510</v>
       </c>
       <c r="F38" s="7">
-        <v>900</v>
+        <v>920</v>
       </c>
       <c r="G38" s="7">
-        <v>600</v>
+        <v>620</v>
       </c>
       <c r="H38" s="7">
-        <v>680</v>
+        <v>700</v>
       </c>
       <c r="I38" s="7">
-        <v>950</v>
+        <v>960</v>
       </c>
       <c r="J38" s="7">
-        <v>860</v>
+        <v>890</v>
       </c>
       <c r="K38" s="7">
-        <v>800</v>
+        <v>830</v>
       </c>
     </row>
     <row r="39" s="1" customFormat="1" ht="18.6655" customHeight="1">
@@ -1509,31 +1513,31 @@
         <v>42</v>
       </c>
       <c r="C39" s="8">
-        <v>39.1</v>
+        <v>42.5</v>
       </c>
       <c r="D39" s="8">
-        <v>1200</v>
+        <v>1350</v>
       </c>
       <c r="E39" s="8">
-        <v>470</v>
+        <v>490</v>
       </c>
       <c r="F39" s="8">
+        <v>900</v>
+      </c>
+      <c r="G39" s="8">
+        <v>600</v>
+      </c>
+      <c r="H39" s="8">
+        <v>680</v>
+      </c>
+      <c r="I39" s="8">
+        <v>950</v>
+      </c>
+      <c r="J39" s="8">
         <v>860</v>
       </c>
-      <c r="G39" s="8">
-        <v>570</v>
-      </c>
-      <c r="H39" s="8">
-        <v>650</v>
-      </c>
-      <c r="I39" s="8">
-        <v>900</v>
-      </c>
-      <c r="J39" s="8">
-        <v>830</v>
-      </c>
       <c r="K39" s="8">
-        <v>780</v>
+        <v>800</v>
       </c>
     </row>
     <row r="40" s="1" customFormat="1" ht="18.6655" customHeight="1">
@@ -1541,31 +1545,31 @@
         <v>43</v>
       </c>
       <c r="C40" s="7">
-        <v>34.5</v>
+        <v>39.1</v>
       </c>
       <c r="D40" s="7">
-        <v>1050</v>
+        <v>1200</v>
       </c>
       <c r="E40" s="7">
-        <v>450</v>
+        <v>470</v>
       </c>
       <c r="F40" s="7">
-        <v>800</v>
+        <v>860</v>
       </c>
       <c r="G40" s="7">
-        <v>525</v>
+        <v>570</v>
       </c>
       <c r="H40" s="7">
-        <v>580</v>
+        <v>650</v>
       </c>
       <c r="I40" s="7">
-        <v>850</v>
+        <v>900</v>
       </c>
       <c r="J40" s="7">
-        <v>810</v>
+        <v>830</v>
       </c>
       <c r="K40" s="7">
-        <v>760</v>
+        <v>780</v>
       </c>
     </row>
     <row r="41" s="1" customFormat="1" ht="18.6655" customHeight="1">
@@ -1573,31 +1577,31 @@
         <v>44</v>
       </c>
       <c r="C41" s="8">
-        <v>31</v>
+        <v>34.5</v>
       </c>
       <c r="D41" s="8">
-        <v>950</v>
+        <v>1050</v>
       </c>
       <c r="E41" s="8">
-        <v>400</v>
+        <v>450</v>
       </c>
       <c r="F41" s="8">
-        <v>750</v>
+        <v>800</v>
       </c>
       <c r="G41" s="8">
-        <v>475</v>
+        <v>525</v>
       </c>
       <c r="H41" s="8">
-        <v>525</v>
+        <v>580</v>
       </c>
       <c r="I41" s="8">
-        <v>800</v>
+        <v>850</v>
       </c>
       <c r="J41" s="8">
+        <v>810</v>
+      </c>
+      <c r="K41" s="8">
         <v>760</v>
-      </c>
-      <c r="K41" s="8">
-        <v>720</v>
       </c>
     </row>
     <row r="42" s="1" customFormat="1" ht="18.6655" customHeight="1">
@@ -1605,31 +1609,31 @@
         <v>45</v>
       </c>
       <c r="C42" s="7">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D42" s="7">
-        <v>840</v>
+        <v>950</v>
       </c>
       <c r="E42" s="7">
-        <v>375</v>
+        <v>400</v>
       </c>
       <c r="F42" s="7">
-        <v>645</v>
+        <v>750</v>
       </c>
       <c r="G42" s="7">
-        <v>395</v>
+        <v>475</v>
       </c>
       <c r="H42" s="7">
-        <v>445</v>
+        <v>525</v>
       </c>
       <c r="I42" s="7">
-        <v>670</v>
+        <v>800</v>
       </c>
       <c r="J42" s="7">
-        <v>670</v>
+        <v>760</v>
       </c>
       <c r="K42" s="7">
-        <v>640</v>
+        <v>720</v>
       </c>
     </row>
     <row r="43" s="1" customFormat="1" ht="18.6655" customHeight="1">
@@ -1637,31 +1641,31 @@
         <v>46</v>
       </c>
       <c r="C43" s="8">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D43" s="8">
-        <v>750</v>
+        <v>840</v>
       </c>
       <c r="E43" s="8">
-        <v>320</v>
+        <v>375</v>
       </c>
       <c r="F43" s="8">
-        <v>580</v>
+        <v>645</v>
       </c>
       <c r="G43" s="8">
-        <v>350</v>
+        <v>395</v>
       </c>
       <c r="H43" s="8">
-        <v>400</v>
+        <v>445</v>
       </c>
       <c r="I43" s="8">
-        <v>600</v>
+        <v>670</v>
       </c>
       <c r="J43" s="8">
-        <v>600</v>
+        <v>670</v>
       </c>
       <c r="K43" s="8">
-        <v>575</v>
+        <v>640</v>
       </c>
     </row>
     <row r="44" s="1" customFormat="1" ht="18.6655" customHeight="1">
@@ -1669,31 +1673,31 @@
         <v>47</v>
       </c>
       <c r="C44" s="7">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D44" s="7">
-        <v>690</v>
+        <v>750</v>
       </c>
       <c r="E44" s="7">
-        <v>295</v>
+        <v>320</v>
       </c>
       <c r="F44" s="7">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="G44" s="7">
-        <v>325</v>
+        <v>350</v>
       </c>
       <c r="H44" s="7">
-        <v>370</v>
+        <v>400</v>
       </c>
       <c r="I44" s="7">
-        <v>530</v>
+        <v>600</v>
       </c>
       <c r="J44" s="7">
+        <v>600</v>
+      </c>
+      <c r="K44" s="7">
         <v>575</v>
-      </c>
-      <c r="K44" s="7">
-        <v>550</v>
       </c>
     </row>
     <row r="45" s="1" customFormat="1" ht="18.6655" customHeight="1">
@@ -1701,31 +1705,31 @@
         <v>48</v>
       </c>
       <c r="C45" s="8">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="D45" s="8">
-        <v>600</v>
+        <v>690</v>
       </c>
       <c r="E45" s="8">
-        <v>250</v>
+        <v>295</v>
       </c>
       <c r="F45" s="8">
-        <v>430</v>
+        <v>500</v>
       </c>
       <c r="G45" s="8">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="H45" s="8">
-        <v>320</v>
+        <v>370</v>
       </c>
       <c r="I45" s="8">
-        <v>450</v>
+        <v>530</v>
       </c>
       <c r="J45" s="8">
-        <v>460</v>
+        <v>575</v>
       </c>
       <c r="K45" s="8">
-        <v>440</v>
+        <v>550</v>
       </c>
     </row>
     <row r="46" s="1" customFormat="1" ht="18.6655" customHeight="1">
@@ -1733,31 +1737,31 @@
         <v>49</v>
       </c>
       <c r="C46" s="7">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="D46" s="7">
-        <v>550</v>
+        <v>600</v>
       </c>
       <c r="E46" s="7">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="F46" s="7">
-        <v>390</v>
+        <v>430</v>
       </c>
       <c r="G46" s="7">
-        <v>260</v>
+        <v>275</v>
       </c>
       <c r="H46" s="7">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="I46" s="7">
-        <v>390</v>
+        <v>450</v>
       </c>
       <c r="J46" s="7">
-        <v>430</v>
+        <v>460</v>
       </c>
       <c r="K46" s="7">
-        <v>415</v>
+        <v>440</v>
       </c>
     </row>
     <row r="47" s="1" customFormat="1" ht="18.6655" customHeight="1">
@@ -1765,28 +1769,28 @@
         <v>50</v>
       </c>
       <c r="C47" s="8">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="D47" s="8">
-        <v>540</v>
+        <v>550</v>
       </c>
       <c r="E47" s="8">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="F47" s="8">
-        <v>370</v>
+        <v>390</v>
       </c>
       <c r="G47" s="8">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="H47" s="8">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="I47" s="8">
-        <v>350</v>
+        <v>390</v>
       </c>
       <c r="J47" s="8">
-        <v>415</v>
+        <v>430</v>
       </c>
       <c r="K47" s="8">
         <v>415</v>
@@ -1797,31 +1801,31 @@
         <v>51</v>
       </c>
       <c r="C48" s="7">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="D48" s="7">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="E48" s="7">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="F48" s="7">
+        <v>370</v>
+      </c>
+      <c r="G48" s="7">
+        <v>255</v>
+      </c>
+      <c r="H48" s="7">
+        <v>290</v>
+      </c>
+      <c r="I48" s="7">
         <v>350</v>
       </c>
-      <c r="G48" s="7">
-        <v>250</v>
-      </c>
-      <c r="H48" s="7">
-        <v>275</v>
-      </c>
-      <c r="I48" s="7">
-        <v>335</v>
-      </c>
       <c r="J48" s="7">
-        <v>400</v>
+        <v>415</v>
       </c>
       <c r="K48" s="7">
-        <v>400</v>
+        <v>415</v>
       </c>
     </row>
     <row r="49" s="1" customFormat="1" ht="18.6655" customHeight="1">
@@ -1829,31 +1833,31 @@
         <v>52</v>
       </c>
       <c r="C49" s="8">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="D49" s="8">
         <v>535</v>
       </c>
       <c r="E49" s="8">
-        <v>195</v>
+        <v>215</v>
       </c>
       <c r="F49" s="8">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="G49" s="8">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="H49" s="8">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="I49" s="8">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="J49" s="8">
-        <v>385</v>
-      </c>
-      <c r="K49" s="8" t="s">
-        <v>11</v>
+        <v>400</v>
+      </c>
+      <c r="K49" s="8">
+        <v>400</v>
       </c>
     </row>
     <row r="50" s="1" customFormat="1" ht="18.6655" customHeight="1">
@@ -1861,28 +1865,28 @@
         <v>53</v>
       </c>
       <c r="C50" s="7">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="D50" s="7">
-        <v>527</v>
+        <v>535</v>
       </c>
       <c r="E50" s="7">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="F50" s="7">
-        <v>315</v>
+        <v>340</v>
       </c>
       <c r="G50" s="7">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="H50" s="7">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="I50" s="7">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="J50" s="7">
-        <v>360</v>
+        <v>385</v>
       </c>
       <c r="K50" s="7" t="s">
         <v>11</v>
@@ -1893,28 +1897,28 @@
         <v>54</v>
       </c>
       <c r="C51" s="8">
-        <v>13</v>
-      </c>
-      <c r="D51" s="8" t="s">
-        <v>11</v>
+        <v>13.5</v>
+      </c>
+      <c r="D51" s="8">
+        <v>527</v>
       </c>
       <c r="E51" s="8">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="F51" s="8">
-        <v>295</v>
+        <v>315</v>
       </c>
       <c r="G51" s="8">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="H51" s="8">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="I51" s="8">
-        <v>250</v>
+        <v>275</v>
       </c>
       <c r="J51" s="8">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="K51" s="8" t="s">
         <v>11</v>
@@ -1934,19 +1938,19 @@
         <v>175</v>
       </c>
       <c r="F52" s="7">
-        <v>270</v>
+        <v>295</v>
       </c>
       <c r="G52" s="7">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="H52" s="7">
-        <v>230</v>
+        <v>245</v>
       </c>
       <c r="I52" s="7">
         <v>250</v>
       </c>
-      <c r="J52" s="7" t="s">
-        <v>11</v>
+      <c r="J52" s="7">
+        <v>355</v>
       </c>
       <c r="K52" s="7" t="s">
         <v>11</v>
@@ -1963,19 +1967,19 @@
         <v>11</v>
       </c>
       <c r="E53" s="8">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="F53" s="8">
-        <v>206</v>
+        <v>270</v>
       </c>
       <c r="G53" s="8">
-        <v>183</v>
+        <v>210</v>
       </c>
       <c r="H53" s="8">
-        <v>198</v>
+        <v>230</v>
       </c>
       <c r="I53" s="8">
-        <v>183</v>
+        <v>250</v>
       </c>
       <c r="J53" s="8" t="s">
         <v>11</v>
@@ -1989,25 +1993,25 @@
         <v>57</v>
       </c>
       <c r="C54" s="7">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="D54" s="7" t="s">
         <v>11</v>
       </c>
       <c r="E54" s="7">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="F54" s="7">
-        <v>190</v>
+        <v>206</v>
       </c>
       <c r="G54" s="7">
-        <v>175</v>
-      </c>
-      <c r="H54" s="7" t="s">
-        <v>11</v>
+        <v>183</v>
+      </c>
+      <c r="H54" s="7">
+        <v>198</v>
       </c>
       <c r="I54" s="7">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="J54" s="7" t="s">
         <v>11</v>
@@ -2021,16 +2025,16 @@
         <v>58</v>
       </c>
       <c r="C55" s="8">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="D55" s="8" t="s">
         <v>11</v>
       </c>
       <c r="E55" s="8">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="F55" s="8">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="G55" s="8">
         <v>175</v>
@@ -2041,8 +2045,8 @@
       <c r="I55" s="8">
         <v>175</v>
       </c>
-      <c r="J55" s="8">
-        <v>245</v>
+      <c r="J55" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="K55" s="8" t="s">
         <v>11</v>
@@ -2053,28 +2057,28 @@
         <v>59</v>
       </c>
       <c r="C56" s="7">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="D56" s="7" t="s">
         <v>11</v>
       </c>
       <c r="E56" s="7">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="F56" s="7">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="G56" s="7">
-        <v>145</v>
+        <v>175</v>
       </c>
       <c r="H56" s="7" t="s">
         <v>11</v>
       </c>
       <c r="I56" s="7">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="J56" s="7">
-        <v>225</v>
+        <v>245</v>
       </c>
       <c r="K56" s="7" t="s">
         <v>11</v>
@@ -2091,81 +2095,114 @@
         <v>11</v>
       </c>
       <c r="E57" s="8">
+        <v>141</v>
+      </c>
+      <c r="F57" s="8">
+        <v>160</v>
+      </c>
+      <c r="G57" s="8">
+        <v>145</v>
+      </c>
+      <c r="H57" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="I57" s="8">
+        <v>165</v>
+      </c>
+      <c r="J57" s="8">
+        <v>225</v>
+      </c>
+      <c r="K57" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="58" s="1" customFormat="1" ht="18.6655" customHeight="1">
+      <c r="B58" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C58" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="D58" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E58" s="7">
         <v>136</v>
       </c>
-      <c r="F57" s="8">
+      <c r="F58" s="7">
         <v>140</v>
       </c>
-      <c r="G57" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H57" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="I57" s="8">
+      <c r="G58" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H58" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I58" s="7">
         <v>150</v>
       </c>
-      <c r="J57" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="K57" s="8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="58" s="1" customFormat="1" ht="18.6655" customHeight="1">
-      <c r="B58" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="C58" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="D58" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="E58" s="10">
+      <c r="J58" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="K58" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="59" s="1" customFormat="1" ht="18.6655" customHeight="1">
+      <c r="B59" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C59" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D59" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E59" s="10">
         <v>135</v>
       </c>
-      <c r="F58" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="G58" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="H58" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="I58" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="J58" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="K58" s="10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="59" s="1" customFormat="1" ht="14.3991" customHeight="1"/>
-    <row r="60" s="1" customFormat="1" ht="151.9905" customHeight="1">
-      <c r="B60" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="C60" s="13"/>
-      <c r="D60" s="13"/>
-      <c r="E60" s="13"/>
-      <c r="F60" s="13"/>
-      <c r="G60" s="13"/>
-      <c r="H60" s="13"/>
-      <c r="I60" s="13"/>
-      <c r="J60" s="13"/>
-      <c r="K60" s="13"/>
-      <c r="L60" s="13"/>
-      <c r="M60" s="13"/>
-    </row>
+      <c r="F59" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G59" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="H59" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="I59" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="J59" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="K59" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="60" s="1" customFormat="1" ht="14.3991" customHeight="1"/>
+    <row r="61" s="1" customFormat="1" ht="151.9905" customHeight="1">
+      <c r="B61" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="C61" s="13"/>
+      <c r="D61" s="13"/>
+      <c r="E61" s="13"/>
+      <c r="F61" s="13"/>
+      <c r="G61" s="13"/>
+      <c r="H61" s="13"/>
+      <c r="I61" s="13"/>
+      <c r="J61" s="13"/>
+      <c r="K61" s="13"/>
+      <c r="L61" s="13"/>
+      <c r="M61" s="13"/>
+    </row>
+    <row r="62" s="1" customFormat="1" ht="28.7982" customHeight="1"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="B2:L2"/>
     <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B60:M60"/>
+    <mergeCell ref="B61:M61"/>
   </mergeCells>
   <pageSetup paperSize="9" scale="100" orientation="landscape"/>
   <headerFooter alignWithMargins="0"/>
